--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -29,8 +29,11 @@
     <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11353,7 +11371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11397,6 +11415,93 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2003_04_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2003_04_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2003_04_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0021 'Baráž o Extraligu' (L15, parent=NODE_S2003_04_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0028</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0028 'Baráž o I.ligu' (L15, parent=NODE_S2003_04_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0041</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0041 'O postup do I.ligy' (L25, parent=NODE_S2003_04_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -14505,8 +14610,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -14586,7 +14689,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -28423,6 +28525,193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0029</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0030</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0031</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2003_04_0021 'Baráž o Extraligu' (L15, parent=NODE_S2003_04_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0028</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2003_04_0028 'Baráž o I.ligu' (L15, parent=NODE_S2003_04_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0041</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2003_04_0041 'O postup do I.ligy' (L25, parent=NODE_S2003_04_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11371,7 +11371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11421,7 +11421,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2003_04_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11433,7 +11433,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2003_04_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11445,7 +11445,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2003_04_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11455,14 +11455,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S2003_04_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0021 'Baráž o Extraligu' (L15, parent=NODE_S2003_04_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11472,14 +11467,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S2003_04_0028</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0028 'Baráž o I.ligu' (L15, parent=NODE_S2003_04_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11489,17 +11479,288 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2003_04_0041</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2003_04_0041 'O postup do I.ligy' (L25, parent=NODE_S2003_04_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -14610,6 +14871,8 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -14640,6 +14903,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0001</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14652,6 +14920,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0003</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14664,6 +14937,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0003</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14676,6 +14954,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0035</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14689,6 +14972,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -20483,12 +20767,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -20782,12 +21066,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -20866,12 +21150,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -21039,12 +21323,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -21123,12 +21407,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21338,12 +21622,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -21469,12 +21753,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -22284,12 +22568,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -22662,12 +22946,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -22788,12 +23072,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -22830,12 +23114,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -23769,12 +24053,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov.</t>
+          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov. || TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>VHS HC Benešov</t>
+          <t>Benešov</t>
         </is>
       </c>
     </row>
@@ -24666,12 +24950,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
+          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram. || TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Junior Mělník</t>
         </is>
       </c>
     </row>
@@ -24834,12 +25118,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -25044,12 +25328,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25212,12 +25496,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -26079,12 +26363,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -27245,12 +27529,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -27944,12 +28228,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -28028,12 +28312,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno.</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
@@ -28531,11 +28815,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -28580,21 +28864,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0029</t>
+          <t>CLUB_S2003_04_0007</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -28602,21 +28884,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0030</t>
+          <t>CLUB_S2003_04_0014</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -28624,21 +28904,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0031</t>
+          <t>CLUB_S2003_04_0016</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -28646,21 +28924,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S2003_04_0021</t>
+          <t>CLUB_S2003_04_0020</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2003_04_0021 'Baráž o Extraligu' (L15, parent=NODE_S2003_04_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -28668,21 +28944,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S2003_04_0028</t>
+          <t>CLUB_S2003_04_0022</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2003_04_0028 'Baráž o I.ligu' (L15, parent=NODE_S2003_04_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -28690,24 +28964,482 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2003_04_0041</t>
+          <t>CLUB_S2003_04_0027</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2003_04_0041 'O postup do I.ligy' (L25, parent=NODE_S2003_04_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0030</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0056</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0061</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0065</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0069</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0070</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0089</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0093</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0114</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0118</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0118</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0123</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0131</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0152</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0154</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0159</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0165</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0171</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0177</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0184</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0187</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0202</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0204</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11371,7 +11371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11433,7 +11433,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11445,7 +11445,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11469,7 +11469,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11481,7 +11481,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11493,7 +11493,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11505,7 +11505,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11517,7 +11517,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11529,7 +11529,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11541,7 +11541,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11553,7 +11553,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11577,7 +11577,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11601,7 +11601,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11613,7 +11613,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11625,7 +11625,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11637,7 +11637,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -11649,118 +11649,10 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -11777,7 +11669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11836,6 +11728,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11878,6 +11775,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Hamé Zlín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11925,6 +11827,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11967,6 +11874,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12009,6 +11921,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12051,6 +11968,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12093,6 +12015,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12135,6 +12062,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12177,6 +12109,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12219,6 +12156,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12261,6 +12203,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12303,6 +12250,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12345,6 +12297,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12387,6 +12344,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12429,6 +12391,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12471,6 +12438,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12513,6 +12485,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12555,6 +12532,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12597,6 +12579,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12639,6 +12626,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12681,6 +12673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12723,6 +12720,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12765,6 +12767,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12807,6 +12814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12849,6 +12861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12891,6 +12908,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12933,6 +12955,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12975,6 +13002,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13064,6 +13096,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13106,6 +13143,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13232,6 +13274,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13274,6 +13321,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13316,6 +13368,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13358,6 +13415,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13400,6 +13462,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13442,6 +13509,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13484,6 +13556,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13526,6 +13603,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13568,6 +13650,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0042</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13610,6 +13697,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0043</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13652,6 +13744,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0044</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13694,6 +13791,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0045</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13736,6 +13838,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13778,6 +13885,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13820,6 +13932,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13862,6 +13979,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13904,6 +14026,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13946,6 +14073,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13988,6 +14120,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14114,6 +14251,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0053</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14240,6 +14382,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0054</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14282,6 +14429,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0055</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -14324,6 +14476,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0056</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -14450,6 +14607,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0061</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -14490,6 +14652,11 @@
       <c r="J64" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0062</t>
         </is>
       </c>
     </row>
@@ -14891,6 +15058,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14908,6 +15080,11 @@
           <t>NODE_S2003_04_0001</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14925,6 +15102,11 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14942,6 +15124,11 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14959,6 +15146,11 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14969,6 +15161,11 @@
       <c r="B82" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -21066,12 +21263,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21323,12 +21520,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21407,12 +21604,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -21622,12 +21819,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24950,12 +25147,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram. || TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Junior Mělník</t>
+          <t>Příbram</t>
         </is>
       </c>
     </row>
@@ -25118,12 +25315,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -25328,12 +25525,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25496,12 +25693,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Stadion Litoměřice</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -27529,12 +27726,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -28815,7 +29012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28889,12 +29086,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0014</t>
+          <t>CLUB_S2003_04_0016</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28909,12 +29106,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0016</t>
+          <t>CLUB_S2003_04_0030</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28929,12 +29126,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0020</t>
+          <t>CLUB_S2003_04_0056</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28949,12 +29146,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0022</t>
+          <t>CLUB_S2003_04_0061</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -28969,12 +29166,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0027</t>
+          <t>CLUB_S2003_04_0065</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28989,12 +29186,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0030</t>
+          <t>CLUB_S2003_04_0069</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29009,12 +29206,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0056</t>
+          <t>CLUB_S2003_04_0070</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29029,12 +29226,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0061</t>
+          <t>CLUB_S2003_04_0089</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -29049,12 +29246,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0065</t>
+          <t>CLUB_S2003_04_0093</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29069,12 +29266,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0069</t>
+          <t>CLUB_S2003_04_0118</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29089,12 +29286,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0070</t>
+          <t>CLUB_S2003_04_0152</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -29109,12 +29306,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0089</t>
+          <t>CLUB_S2003_04_0154</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29129,12 +29326,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0093</t>
+          <t>CLUB_S2003_04_0159</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -29149,12 +29346,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0114</t>
+          <t>CLUB_S2003_04_0165</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Příbram' → 'Junior Mělník' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -29169,12 +29366,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0118</t>
+          <t>CLUB_S2003_04_0171</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -29189,12 +29386,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0118</t>
+          <t>CLUB_S2003_04_0177</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -29209,12 +29406,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0123</t>
+          <t>CLUB_S2003_04_0187</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -29229,12 +29426,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0131</t>
+          <t>CLUB_S2003_04_0202</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29249,197 +29446,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2003_04_0152</t>
+          <t>CLUB_S2003_04_0204</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0154</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0159</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0165</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0171</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0177</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0184</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0187</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0202</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2003_04_0204</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -11669,7 +11669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11733,6 +11733,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15038,8 +15048,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -15169,7 +15177,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -11921,6 +11921,16 @@
           <t>NODE_S2003_04_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11935,6 +11945,14 @@
         <is>
           <t>NODE_S2002_03_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12109,6 +12127,16 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12123,6 +12151,14 @@
         <is>
           <t>NODE_S2002_03_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -12203,6 +12239,16 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12217,6 +12263,14 @@
         <is>
           <t>NODE_S2002_03_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -12250,6 +12304,16 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12264,6 +12328,14 @@
         <is>
           <t>NODE_S2002_03_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -12297,6 +12369,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12311,6 +12385,14 @@
         <is>
           <t>NODE_S2002_03_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -12344,6 +12426,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12358,6 +12442,14 @@
         <is>
           <t>NODE_S2002_03_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -12391,6 +12483,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12405,6 +12499,14 @@
         <is>
           <t>NODE_S2002_03_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -12438,6 +12540,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12452,6 +12556,14 @@
         <is>
           <t>NODE_S2002_03_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -12485,6 +12597,8 @@
           <t>NODE_S2003_04_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12499,6 +12613,14 @@
         <is>
           <t>NODE_S2002_03_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -12532,6 +12654,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12546,6 +12670,14 @@
         <is>
           <t>NODE_S2002_03_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -12579,6 +12711,8 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12593,6 +12727,14 @@
         <is>
           <t>NODE_S2002_03_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -12626,6 +12768,16 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12640,6 +12792,14 @@
         <is>
           <t>NODE_S2002_03_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -12767,6 +12927,16 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12781,6 +12951,14 @@
         <is>
           <t>NODE_S2002_03_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -12814,6 +12992,16 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12828,6 +13016,14 @@
         <is>
           <t>NODE_S2002_03_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -12861,6 +13057,12 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12875,6 +13077,14 @@
         <is>
           <t>NODE_S2002_03_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -12908,6 +13118,12 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12922,6 +13138,14 @@
         <is>
           <t>NODE_S2002_03_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -12955,6 +13179,8 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12969,6 +13195,14 @@
         <is>
           <t>NODE_S2002_03_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -13002,6 +13236,8 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13016,6 +13252,14 @@
         <is>
           <t>NODE_S2002_03_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -13509,6 +13753,12 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0039</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13523,6 +13773,14 @@
         <is>
           <t>NODE_S2002_03_0039</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -13556,6 +13814,12 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13570,6 +13834,14 @@
         <is>
           <t>NODE_S2002_03_0040</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -13603,6 +13875,8 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13617,6 +13891,14 @@
         <is>
           <t>NODE_S2002_03_0041</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -13744,6 +14026,8 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13758,6 +14042,14 @@
         <is>
           <t>NODE_S2002_03_0044</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -13885,6 +14177,12 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0038</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13899,6 +14197,14 @@
         <is>
           <t>NODE_S2002_03_0047</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -14026,6 +14332,12 @@
           <t>NODE_S2003_04_0048</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0050</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14040,6 +14352,14 @@
         <is>
           <t>NODE_S2002_03_0050</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -14073,6 +14393,8 @@
           <t>NODE_S2003_04_0048</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14087,6 +14409,14 @@
         <is>
           <t>NODE_S2002_03_0051</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -14167,6 +14497,12 @@
           <t>NODE_S2003_04_0051</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14176,6 +14512,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4 týmů</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -14209,6 +14553,8 @@
           <t>NODE_S2003_04_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14218,6 +14564,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -14298,6 +14652,12 @@
           <t>NODE_S2003_04_0054</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0056</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14307,6 +14667,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -14340,6 +14708,8 @@
           <t>NODE_S2003_04_0054</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14349,6 +14719,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -14471,6 +14849,16 @@
           <t>REG_VYC</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0061</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14490,6 +14878,14 @@
         <is>
           <t>NODE_S2002_03_0056</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>16 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -14523,6 +14919,8 @@
           <t>NODE_S2003_04_0059</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14532,6 +14930,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -14565,6 +14971,8 @@
           <t>NODE_S2003_04_0059</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14574,6 +14982,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>-2.–16. ZČ</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -14654,6 +15070,12 @@
           <t>NODE_S2003_04_0062</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0065</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14668,6 +15090,14 @@
         <is>
           <t>NODE_S2002_03_0062</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14701,6 +15131,8 @@
           <t>NODE_S2003_04_0062</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14710,6 +15142,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -14743,6 +15183,8 @@
           <t>NODE_S2003_04_0062</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14752,6 +15194,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -14911,6 +15361,12 @@
           <t>NODE_S2003_04_0068</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0070</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14920,6 +15376,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -14953,6 +15417,8 @@
           <t>NODE_S2003_04_0068</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14962,6 +15428,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -15048,6 +15522,8 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -15177,6 +15653,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -830,6 +830,11 @@
           <t>HC Hamé Zlín (C)</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
@@ -12369,8 +12374,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12426,8 +12429,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12483,8 +12484,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12540,8 +12539,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12597,8 +12594,6 @@
           <t>NODE_S2003_04_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12654,8 +12649,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12711,8 +12704,6 @@
           <t>NODE_S2003_04_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13062,7 +13053,6 @@
           <t>NODE_S2003_04_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13123,7 +13113,6 @@
           <t>NODE_S2003_04_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13179,8 +13168,6 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13236,8 +13223,6 @@
           <t>NODE_S2003_04_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13758,7 +13743,6 @@
           <t>NODE_S2003_04_0039</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13819,7 +13803,6 @@
           <t>NODE_S2003_04_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13875,8 +13858,6 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14026,8 +14007,6 @@
           <t>NODE_S2003_04_0035</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14182,7 +14161,6 @@
           <t>NODE_S2003_04_0038</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14337,7 +14315,6 @@
           <t>NODE_S2003_04_0050</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14393,8 +14370,6 @@
           <t>NODE_S2003_04_0048</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14502,7 +14477,6 @@
           <t>NODE_S2003_04_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14553,8 +14527,6 @@
           <t>NODE_S2003_04_0051</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14657,7 +14629,6 @@
           <t>NODE_S2003_04_0056</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14708,8 +14679,6 @@
           <t>NODE_S2003_04_0054</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14919,8 +14888,6 @@
           <t>NODE_S2003_04_0059</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14971,8 +14938,6 @@
           <t>NODE_S2003_04_0059</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15075,7 +15040,6 @@
           <t>NODE_S2003_04_0065</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15131,8 +15095,6 @@
           <t>NODE_S2003_04_0062</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15183,8 +15145,6 @@
           <t>NODE_S2003_04_0062</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15366,7 +15326,6 @@
           <t>NODE_S2003_04_0070</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15417,8 +15376,6 @@
           <t>NODE_S2003_04_0068</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15522,8 +15479,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -15653,7 +15608,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -29302,7 +29256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29482,6 +29436,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Hamé Zlín</t>
         </is>
       </c>
     </row>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -15479,6 +15479,8 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -15608,6 +15610,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -3732,7 +3732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7384,6 +7384,568 @@
       <c r="V48" t="inlineStr">
         <is>
           <t>TR_S2003_04_00233</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0253</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0254</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0255</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0256</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0257</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0258</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0259</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0260</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0261</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00313</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0262</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0263</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0264</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00316</t>
         </is>
       </c>
     </row>
@@ -8692,7 +9254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8910,6 +9472,658 @@
       <c r="U3" s="2" t="n"/>
       <c r="V3" s="2" t="n"/>
       <c r="W3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0265</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Reinpo Auto</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0266</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HC Vatín-HOGR</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0267</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0268</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0269</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0270</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0271</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0272</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0273</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0274</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0275</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00327</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0276</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00328</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0277</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00329</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0278</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9078,7 +10292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10356,6 +11570,478 @@
       <c r="U24" s="2" t="n"/>
       <c r="V24" s="2" t="n"/>
       <c r="W24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0279</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00331</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0280</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00332</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>U Bláhovky Brno</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0281</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00333</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0282</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00334</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TJ Sokol Domašov-Říčky</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0283</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00335</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0284</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00336</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TJ Tatran Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0285</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00337</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AC Lelekovice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0286</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00338</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HC Orel Čebín</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0287</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HC Juliánov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0288</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11674,7 +13360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15636,6 +17322,191 @@
       <c r="A87" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Středočeský – Kladno</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0047</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Jihočeský – Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0048</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0075</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Východočeský – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0059</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0076</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Vysočina – Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0066</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0077</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Brno Venkov</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0068</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -21062,7 +22933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J195"/>
+  <dimension ref="A1:J272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -29245,6 +31116,2470 @@
       <c r="J195" t="inlineStr">
         <is>
           <t>Studénka</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0212</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Kladno 1988 B</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Kladno 1988 B</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0213</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0214</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0215</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ford VaM Kladno</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ford VaM Kladno</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0216</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Velc Žilina</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Velc Žilina</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0217</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0218</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0219</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0220</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0221</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0222</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0223</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0224</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Kralovice</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Kralovice</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0225</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0226</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0227</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0228</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0229</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0230</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0231</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0232</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0233</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0234</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0235</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0236</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0237</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0238</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0239</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0240</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0241</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0242</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0243</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0244</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0245</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0246</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights C</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights C</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0247</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0248</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0249</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0250</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0251</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0252</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>B-Praktik ČK/Přísečná</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>B-Praktik ČK/Přísečná</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0253</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0254</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0255</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0256</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0257</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0258</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0259</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0260</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0261</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0262</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0263</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0264</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0265</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0266</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Reinpo Auto</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Reinpo Auto</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0267</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HC Vatín-HOGR</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HC Vatín-HOGR</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0268</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0269</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0270</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0271</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0272</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0273</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0274</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0275</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0276</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0277</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0278</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0279</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0280</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0281</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>U Bláhovky Brno</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>U Bláhovky Brno</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0282</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0283</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TJ Sokol Domašov-Říčky</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TJ Sokol Domašov-Říčky</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0284</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0285</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TJ Tatran Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TJ Tatran Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0286</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>AC Lelekovice</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>AC Lelekovice</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0287</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HC Orel Čebín</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>HC Orel Čebín</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0288</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HC Juliánov</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HC Juliánov</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -37890,7 +42225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -40104,6 +44439,739 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kladno 1988 B</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0212</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0213</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0214</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ford VaM Kladno</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0215</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Velc Žilina</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0216</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0217</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0218</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0219</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0220</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0221</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0222</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0223</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kralovice</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0224</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0225</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0226</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0073</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0227</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00279</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40115,7 +45183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -41618,6 +46686,1153 @@
       <c r="V28" t="inlineStr">
         <is>
           <t>SER_S2003_04_0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0228</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0229</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0230</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0231</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0232</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0233</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0234</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0235</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0236</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0237</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0238</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0239</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0240</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0241</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0242</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0243</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0244</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0245</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights C</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0246</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0247</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0248</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0249</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0250</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0251</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B-Praktik ČK/Přísečná</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2003_04_0074</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2003_04_0252</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2003_04_00304</t>
         </is>
       </c>
     </row>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -17165,8 +17165,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -17296,7 +17294,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -33857,7 +33854,7 @@
           <t>CLUB_S2003_04_0007</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33877,7 +33874,7 @@
           <t>CLUB_S2003_04_0016</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33897,7 +33894,7 @@
           <t>CLUB_S2003_04_0030</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33917,7 +33914,7 @@
           <t>CLUB_S2003_04_0056</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -33937,7 +33934,7 @@
           <t>CLUB_S2003_04_0061</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -33957,7 +33954,7 @@
           <t>CLUB_S2003_04_0065</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33977,7 +33974,7 @@
           <t>CLUB_S2003_04_0069</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33997,7 +33994,7 @@
           <t>CLUB_S2003_04_0070</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34017,7 +34014,7 @@
           <t>CLUB_S2003_04_0089</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -34037,7 +34034,7 @@
           <t>CLUB_S2003_04_0093</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34057,7 +34054,7 @@
           <t>CLUB_S2003_04_0118</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34077,7 +34074,7 @@
           <t>CLUB_S2003_04_0152</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -34097,7 +34094,7 @@
           <t>CLUB_S2003_04_0154</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34117,7 +34114,7 @@
           <t>CLUB_S2003_04_0159</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0145 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -34137,7 +34134,7 @@
           <t>CLUB_S2003_04_0165</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34157,7 +34154,7 @@
           <t>CLUB_S2003_04_0171</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -34177,7 +34174,7 @@
           <t>CLUB_S2003_04_0177</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2002_03_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -34197,7 +34194,7 @@
           <t>CLUB_S2003_04_0187</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34217,7 +34214,7 @@
           <t>CLUB_S2003_04_0202</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34237,7 +34234,7 @@
           <t>CLUB_S2003_04_0204</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -15035,7 +15035,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finále</t>
+          <t>Jihočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Ústecký L40 základní část</t>
+          <t>Ústecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Ústecký L40 finále</t>
+          <t>Ústecký, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 finále</t>
+          <t>Liberecký, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 o udržení</t>
+          <t>Východočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Zlínský L40</t>
+          <t>Zlínský, 4. úroveň</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Zlínský L40 základní část</t>
+          <t>Zlínský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Zlínský L40 skupina o 5.-7.místo</t>
+          <t>Zlínský, 4. úroveň, skupina o 5.-7.místo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Zlínský L40 finále</t>
+          <t>Zlínský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Olomoucký L40</t>
+          <t>Olomoucký, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní skupina</t>
+          <t>Jihomoravský, 4. úroveň, základní skupina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Moravskoslezský L40</t>
+          <t>Moravskoslezský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Moravskoslezský L40 základní část</t>
+          <t>Moravskoslezský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17165,6 +17165,8 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -17197,7 +17199,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -17294,6 +17296,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>

--- a/data/S2003_04_FINAL.xlsx
+++ b/data/S2003_04_FINAL.xlsx
@@ -6253,7 +6253,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -17165,8 +17165,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -17296,7 +17294,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -17813,7 +17810,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -17891,7 +17888,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -17969,7 +17966,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -18047,7 +18044,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -18130,7 +18127,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -18208,7 +18205,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -18286,7 +18283,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -18364,7 +18361,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -18442,7 +18439,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -18525,7 +18522,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -18603,7 +18600,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -18681,7 +18678,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -18759,7 +18756,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -18842,7 +18839,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -19292,7 +19289,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -19370,7 +19367,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -19448,7 +19445,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -19526,7 +19523,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -35171,7 +35168,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -35249,7 +35246,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -35327,7 +35324,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -35405,7 +35402,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -35520,7 +35517,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -35598,7 +35595,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -35676,7 +35673,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -35754,7 +35751,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -36847,7 +36844,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -36925,7 +36922,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -37003,7 +37000,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -37081,7 +37078,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -38738,7 +38735,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -38816,7 +38813,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -38894,7 +38891,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -40784,7 +40781,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -40862,7 +40859,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -40940,7 +40937,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -41018,7 +41015,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -41247,7 +41244,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -41325,7 +41322,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -41403,7 +41400,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -48749,7 +48746,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -48827,7 +48824,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -48905,7 +48902,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -48988,7 +48985,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
